--- a/artfynd/S 6659-2021 artfynd.xlsx
+++ b/artfynd/S 6659-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82284234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82523116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82523117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102648642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86622945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86622955</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86622977</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82523115</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,6 +1876,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125644642</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231333</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2066,6 +2126,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110397837</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2193,6 +2258,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82662187</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2320,6 +2390,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82662180</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2428,6 +2503,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83064313</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,8 +2633,31 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89086098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 6659-2021 artfynd.xlsx
+++ b/artfynd/S 6659-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1884,32 +1884,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106231333</v>
+        <v>136171923</v>
       </c>
       <c r="B12" t="n">
-        <v>9596</v>
+        <v>9417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101479</v>
+        <v>101246</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1917,24 +1917,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tomtevägen, Bl</t>
+          <t>Hässlegården, Bl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540992</v>
+        <v>541020</v>
       </c>
       <c r="R12" t="n">
-        <v>6230209</v>
+        <v>6230144</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1958,17 +1953,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Epost från Peter o Gull-Britt Hermansson Haglund , med foto</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,31 +1982,30 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Forslund</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Markus Forslund</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106231333</t>
+          <t>https://artportalen.se/Sighting/136171923</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110397837</v>
+        <v>106231333</v>
       </c>
       <c r="B13" t="n">
         <v>9596</v>
@@ -2034,37 +2038,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tomtevägen 1, Bl</t>
+          <t>Tomtevägen, Bl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540986</v>
+        <v>540992</v>
       </c>
       <c r="R13" t="n">
-        <v>6230223</v>
+        <v>6230209</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2101,7 +2089,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Observerad av fastighetsägaren. Säkert artbestämd via bild (som tyvärr inte är tillgänglig längre).</t>
+          <t>Epost från Peter o Gull-Britt Hermansson Haglund , med foto</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,49 +2105,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marcus Törnberg</t>
+          <t>Markus Forslund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Marcus Törnberg</t>
+          <t>Via Markus Forslund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110397837</t>
+          <t>https://artportalen.se/Sighting/106231333</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>82662187</v>
+        <v>110397837</v>
       </c>
       <c r="B14" t="n">
-        <v>57947</v>
+        <v>9596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>101479</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2167,15 +2155,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2K+</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2185,17 +2178,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spandelstorpsskolans parkering, Bl</t>
+          <t>Tomtevägen 1, Bl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540493</v>
+        <v>540986</v>
       </c>
       <c r="R14" t="n">
-        <v>6230209</v>
+        <v>6230223</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +2212,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-03-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-03-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Observerad av fastighetsägaren. Säkert artbestämd via bild (som tyvärr inte är tillgänglig längre).</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,55 +2231,56 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Lindberg</t>
+          <t>Marcus Törnberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Lindberg</t>
+          <t>Via Marcus Törnberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82662187</t>
+          <t>https://artportalen.se/Sighting/110397837</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82662180</v>
+        <v>82662187</v>
       </c>
       <c r="B15" t="n">
-        <v>58112</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2392,16 +2381,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82662180</t>
+          <t>https://artportalen.se/Sighting/82662187</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83064313</v>
+        <v>82662180</v>
       </c>
       <c r="B16" t="n">
-        <v>8369</v>
+        <v>58112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,42 +2398,57 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>103020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra gärde, Bl</t>
+          <t>Spandelstorpsskolans parkering, Bl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540902</v>
+        <v>540493</v>
       </c>
       <c r="R16" t="n">
-        <v>6230084</v>
+        <v>6230209</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2468,17 +2472,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2020-03-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Vindfälld ask. Äldre gnagspår</t>
+          <t>2020-03-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,77 +2496,73 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Tommy Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Tommy Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83064313</t>
+          <t>https://artportalen.se/Sighting/82662180</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89086098</v>
+        <v>83064313</v>
       </c>
       <c r="B17" t="n">
-        <v>107340</v>
+        <v>8369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224265</v>
+        <v>106540</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äkta hjärtstilla</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leonurus cardiaca subsp. cardiaca</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hässlegården, Bl</t>
+          <t>Västra gärde, Bl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541148</v>
+        <v>540902</v>
       </c>
       <c r="R17" t="n">
-        <v>6230239</v>
+        <v>6230084</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2582,24 +2587,19 @@
           <t>Augerum</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>K-Kna-1892</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Åtminstone ca 80 'tuvor'. Stjälkar tresiffrigt. Samtliga i hästhagen N-NO boningshuset.</t>
+          <t>Vindfälld ask. Äldre gnagspår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,28 +2612,149 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>hästhage</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Niclas Wahlgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niclas Wahlgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83064313</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89086098</v>
+      </c>
+      <c r="B18" t="n">
+        <v>107340</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224265</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Äkta hjärtstilla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leonurus cardiaca subsp. cardiaca</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hässlegården, Bl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>541148</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6230239</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Augerum</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>K-Kna-1892</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Åtminstone ca 80 'tuvor'. Stjälkar tresiffrigt. Samtliga i hästhagen N-NO boningshuset.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>hästhage</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Åke Widgren</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Jonas Hjelm</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89086098</t>
         </is>
@@ -2657,6 +2778,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
